--- a/data/QTTY/Gold/combine.xlsx
+++ b/data/QTTY/Gold/combine.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CLC\ASA-Experiments\data\QTTY\Gold\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\HCMUS\Thesis\Automatic Sentence Alignment\data\QTTY\Gold\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73AE347-6C7A-408D-9039-6551037E3106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0607207-CC93-4BEF-8073-69950F68764C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="6270" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -10131,9 +10131,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C1086"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="51.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10144,7 +10147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -10155,7 +10158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -10166,7 +10169,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -10177,7 +10180,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -10188,7 +10191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -10199,7 +10202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -10210,7 +10213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -10221,7 +10224,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -10232,7 +10235,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -10243,7 +10246,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -10254,7 +10257,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -10265,7 +10268,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -10276,7 +10279,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -10287,7 +10290,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -10298,7 +10301,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -10309,7 +10312,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -10320,7 +10323,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -10331,7 +10334,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -10342,7 +10345,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -10353,7 +10356,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -10364,7 +10367,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -10375,7 +10378,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -10386,7 +10389,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -10397,7 +10400,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -10408,7 +10411,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -10419,7 +10422,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -10430,7 +10433,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -10441,7 +10444,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -10452,7 +10455,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -10463,7 +10466,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -10474,7 +10477,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -10485,7 +10488,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -10496,7 +10499,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -10507,7 +10510,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -10518,7 +10521,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>105</v>
       </c>
@@ -10529,7 +10532,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -10540,7 +10543,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -10551,7 +10554,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>114</v>
       </c>
@@ -10562,7 +10565,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -10573,7 +10576,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -10584,7 +10587,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -10595,7 +10598,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -10606,7 +10609,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -10617,7 +10620,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -10628,7 +10631,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>135</v>
       </c>
@@ -10639,7 +10642,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -10650,7 +10653,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -10661,7 +10664,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -10672,7 +10675,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>147</v>
       </c>
@@ -10683,7 +10686,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -10694,7 +10697,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -10705,7 +10708,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>156</v>
       </c>
@@ -10716,7 +10719,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -10727,7 +10730,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>162</v>
       </c>
@@ -10738,7 +10741,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -10749,7 +10752,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -10760,7 +10763,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -10771,7 +10774,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>174</v>
       </c>
@@ -10782,7 +10785,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>177</v>
       </c>
@@ -10793,7 +10796,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>180</v>
       </c>
@@ -10804,7 +10807,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>183</v>
       </c>
@@ -10815,7 +10818,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>186</v>
       </c>
@@ -10826,7 +10829,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>189</v>
       </c>
@@ -10837,7 +10840,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>192</v>
       </c>
@@ -10848,7 +10851,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>195</v>
       </c>
@@ -10859,7 +10862,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>198</v>
       </c>
@@ -10870,7 +10873,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>201</v>
       </c>
@@ -10881,7 +10884,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>204</v>
       </c>
@@ -10892,7 +10895,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>207</v>
       </c>
@@ -10903,7 +10906,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>210</v>
       </c>
@@ -10914,7 +10917,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>213</v>
       </c>
@@ -10925,7 +10928,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>216</v>
       </c>
@@ -10936,7 +10939,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>219</v>
       </c>
@@ -10947,7 +10950,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>222</v>
       </c>
@@ -10958,7 +10961,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>225</v>
       </c>
@@ -10969,7 +10972,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>228</v>
       </c>
@@ -10980,7 +10983,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>231</v>
       </c>
@@ -10991,7 +10994,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>234</v>
       </c>
@@ -11002,7 +11005,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>237</v>
       </c>
@@ -11013,7 +11016,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>240</v>
       </c>
@@ -11024,7 +11027,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>243</v>
       </c>
@@ -11035,7 +11038,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>246</v>
       </c>
@@ -11046,7 +11049,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>249</v>
       </c>
@@ -11057,7 +11060,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>252</v>
       </c>
@@ -11068,7 +11071,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>255</v>
       </c>
@@ -11079,7 +11082,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>258</v>
       </c>
@@ -11090,7 +11093,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>261</v>
       </c>
@@ -11101,7 +11104,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>264</v>
       </c>
@@ -11112,7 +11115,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>267</v>
       </c>
@@ -11123,7 +11126,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>270</v>
       </c>
@@ -11134,7 +11137,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>273</v>
       </c>
@@ -11145,7 +11148,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>276</v>
       </c>
@@ -11156,7 +11159,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>279</v>
       </c>
@@ -11167,7 +11170,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>282</v>
       </c>
@@ -11178,7 +11181,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>285</v>
       </c>
@@ -11189,7 +11192,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>288</v>
       </c>
@@ -11200,7 +11203,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>291</v>
       </c>
@@ -11211,7 +11214,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>294</v>
       </c>
@@ -11222,7 +11225,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>297</v>
       </c>
@@ -11233,7 +11236,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>300</v>
       </c>
@@ -11244,7 +11247,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>303</v>
       </c>
@@ -11255,7 +11258,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>306</v>
       </c>
@@ -11266,7 +11269,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>309</v>
       </c>
@@ -11277,7 +11280,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>312</v>
       </c>
@@ -11288,7 +11291,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>315</v>
       </c>
@@ -11299,7 +11302,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>318</v>
       </c>
@@ -11310,7 +11313,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>321</v>
       </c>
@@ -11321,7 +11324,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>324</v>
       </c>
@@ -11332,7 +11335,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>327</v>
       </c>
@@ -11343,7 +11346,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>330</v>
       </c>
@@ -11354,7 +11357,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>333</v>
       </c>
@@ -11365,7 +11368,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>336</v>
       </c>
@@ -11376,7 +11379,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>339</v>
       </c>
@@ -11387,7 +11390,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>342</v>
       </c>
@@ -11398,7 +11401,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>345</v>
       </c>
@@ -11409,7 +11412,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>348</v>
       </c>
@@ -11420,7 +11423,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>351</v>
       </c>
@@ -11431,7 +11434,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>354</v>
       </c>
@@ -11442,7 +11445,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>357</v>
       </c>
@@ -11453,7 +11456,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>360</v>
       </c>
@@ -11464,7 +11467,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>363</v>
       </c>
@@ -11475,7 +11478,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>366</v>
       </c>
@@ -11486,7 +11489,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>369</v>
       </c>
@@ -11497,7 +11500,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>372</v>
       </c>
@@ -11508,7 +11511,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>375</v>
       </c>
@@ -11519,7 +11522,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>378</v>
       </c>
@@ -11530,7 +11533,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>381</v>
       </c>
@@ -11541,7 +11544,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>384</v>
       </c>
@@ -11552,7 +11555,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>387</v>
       </c>
@@ -11563,7 +11566,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>390</v>
       </c>
@@ -11574,7 +11577,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>393</v>
       </c>
@@ -11585,7 +11588,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>396</v>
       </c>
@@ -11596,7 +11599,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>399</v>
       </c>
@@ -11607,7 +11610,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>402</v>
       </c>
@@ -11618,7 +11621,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>405</v>
       </c>
@@ -11629,7 +11632,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>408</v>
       </c>
@@ -11640,7 +11643,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>411</v>
       </c>
@@ -11651,7 +11654,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>414</v>
       </c>
@@ -11662,7 +11665,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>417</v>
       </c>
@@ -11673,7 +11676,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>420</v>
       </c>
@@ -11684,7 +11687,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>423</v>
       </c>
@@ -11695,7 +11698,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>426</v>
       </c>
@@ -11706,7 +11709,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>429</v>
       </c>
@@ -11717,7 +11720,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>432</v>
       </c>
@@ -11728,7 +11731,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>435</v>
       </c>
@@ -11739,7 +11742,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>438</v>
       </c>
@@ -11750,7 +11753,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>441</v>
       </c>
@@ -11761,7 +11764,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>444</v>
       </c>
@@ -11772,7 +11775,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>447</v>
       </c>
@@ -11783,7 +11786,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>450</v>
       </c>
@@ -11794,7 +11797,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>453</v>
       </c>
@@ -11805,7 +11808,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>456</v>
       </c>
@@ -11816,7 +11819,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>459</v>
       </c>
@@ -11827,7 +11830,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>462</v>
       </c>
@@ -11838,7 +11841,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>465</v>
       </c>
@@ -11849,7 +11852,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>468</v>
       </c>
@@ -11860,7 +11863,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>471</v>
       </c>
@@ -11871,7 +11874,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>474</v>
       </c>
@@ -11882,7 +11885,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>477</v>
       </c>
@@ -11893,7 +11896,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>480</v>
       </c>
@@ -11904,7 +11907,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>483</v>
       </c>
@@ -11915,7 +11918,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>486</v>
       </c>
@@ -11926,7 +11929,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>489</v>
       </c>
@@ -11937,7 +11940,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>492</v>
       </c>
@@ -11948,7 +11951,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>495</v>
       </c>
@@ -11959,7 +11962,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>498</v>
       </c>
@@ -11970,7 +11973,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>501</v>
       </c>
@@ -11981,7 +11984,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>504</v>
       </c>
@@ -11992,7 +11995,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>507</v>
       </c>
@@ -12003,7 +12006,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>510</v>
       </c>
@@ -12014,7 +12017,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>513</v>
       </c>
@@ -12025,7 +12028,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>516</v>
       </c>
@@ -12036,7 +12039,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>519</v>
       </c>
@@ -12047,7 +12050,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>522</v>
       </c>
@@ -12058,7 +12061,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>525</v>
       </c>
@@ -12069,7 +12072,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>528</v>
       </c>
@@ -12080,7 +12083,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>531</v>
       </c>
@@ -12091,7 +12094,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>534</v>
       </c>
@@ -12102,7 +12105,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>537</v>
       </c>
@@ -12113,7 +12116,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>540</v>
       </c>
@@ -12124,7 +12127,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>543</v>
       </c>
@@ -12135,7 +12138,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>546</v>
       </c>
@@ -12146,7 +12149,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>549</v>
       </c>
@@ -12157,7 +12160,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>552</v>
       </c>
@@ -12168,7 +12171,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>555</v>
       </c>
@@ -12179,7 +12182,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>558</v>
       </c>
@@ -12190,7 +12193,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>561</v>
       </c>
@@ -12201,7 +12204,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>564</v>
       </c>
@@ -12212,7 +12215,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>567</v>
       </c>
@@ -12223,7 +12226,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>570</v>
       </c>
@@ -12234,7 +12237,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>573</v>
       </c>
@@ -12245,7 +12248,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>576</v>
       </c>
@@ -12256,7 +12259,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>579</v>
       </c>
@@ -12267,7 +12270,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>582</v>
       </c>
@@ -12278,7 +12281,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>585</v>
       </c>
@@ -12289,7 +12292,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>588</v>
       </c>
@@ -12300,7 +12303,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>591</v>
       </c>
@@ -12311,7 +12314,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>594</v>
       </c>
@@ -12322,7 +12325,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>597</v>
       </c>
@@ -12333,7 +12336,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>600</v>
       </c>
@@ -12344,7 +12347,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>603</v>
       </c>
@@ -12355,7 +12358,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>606</v>
       </c>
@@ -12366,7 +12369,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>609</v>
       </c>
@@ -12377,7 +12380,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>612</v>
       </c>
@@ -12388,7 +12391,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>615</v>
       </c>
@@ -12399,7 +12402,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>618</v>
       </c>
@@ -12410,7 +12413,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>621</v>
       </c>
@@ -12421,7 +12424,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>624</v>
       </c>
@@ -12432,7 +12435,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>627</v>
       </c>
@@ -12443,7 +12446,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>630</v>
       </c>
@@ -12454,7 +12457,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>633</v>
       </c>
@@ -12465,7 +12468,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>636</v>
       </c>
@@ -12476,7 +12479,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>639</v>
       </c>
@@ -12487,7 +12490,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>642</v>
       </c>
@@ -12498,7 +12501,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>645</v>
       </c>
@@ -12509,7 +12512,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>648</v>
       </c>
@@ -12520,7 +12523,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>651</v>
       </c>
@@ -12531,7 +12534,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>654</v>
       </c>
@@ -12542,7 +12545,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>657</v>
       </c>
@@ -12553,7 +12556,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>660</v>
       </c>
@@ -12564,7 +12567,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>663</v>
       </c>
@@ -12575,7 +12578,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>666</v>
       </c>
@@ -12586,7 +12589,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>669</v>
       </c>
@@ -12597,7 +12600,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>672</v>
       </c>
@@ -12608,7 +12611,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>675</v>
       </c>
@@ -12619,7 +12622,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>678</v>
       </c>
@@ -12630,7 +12633,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>681</v>
       </c>
@@ -12641,7 +12644,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>684</v>
       </c>
@@ -12652,7 +12655,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>687</v>
       </c>
@@ -12663,7 +12666,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>690</v>
       </c>
@@ -12674,7 +12677,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>693</v>
       </c>
@@ -12685,7 +12688,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>696</v>
       </c>
@@ -12696,7 +12699,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>699</v>
       </c>
@@ -12707,7 +12710,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>702</v>
       </c>
@@ -12718,7 +12721,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>705</v>
       </c>
@@ -12729,7 +12732,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>708</v>
       </c>
@@ -12740,7 +12743,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>711</v>
       </c>
@@ -12751,7 +12754,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>714</v>
       </c>
@@ -12762,7 +12765,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>717</v>
       </c>
@@ -12773,7 +12776,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>720</v>
       </c>
@@ -12784,7 +12787,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>723</v>
       </c>
@@ -12795,7 +12798,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>726</v>
       </c>
@@ -12806,7 +12809,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>729</v>
       </c>
@@ -12817,7 +12820,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>732</v>
       </c>
@@ -12828,7 +12831,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>735</v>
       </c>
@@ -12839,7 +12842,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>738</v>
       </c>
@@ -12850,7 +12853,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>741</v>
       </c>
@@ -12861,7 +12864,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>744</v>
       </c>
@@ -12872,7 +12875,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>747</v>
       </c>
@@ -12883,7 +12886,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>750</v>
       </c>
@@ -12894,7 +12897,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>753</v>
       </c>
@@ -12905,7 +12908,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>756</v>
       </c>
@@ -12916,7 +12919,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>759</v>
       </c>
@@ -12927,7 +12930,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>762</v>
       </c>
@@ -12938,7 +12941,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>765</v>
       </c>
@@ -12949,7 +12952,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>768</v>
       </c>
@@ -12960,7 +12963,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>771</v>
       </c>
@@ -12971,7 +12974,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>774</v>
       </c>
@@ -12982,7 +12985,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>777</v>
       </c>
@@ -12993,7 +12996,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>780</v>
       </c>
@@ -13004,7 +13007,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>783</v>
       </c>
@@ -13015,7 +13018,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>786</v>
       </c>
@@ -13026,7 +13029,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>789</v>
       </c>
@@ -13037,7 +13040,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>792</v>
       </c>
@@ -13048,7 +13051,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>795</v>
       </c>
@@ -13059,7 +13062,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>798</v>
       </c>
@@ -13070,7 +13073,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>801</v>
       </c>
@@ -13081,7 +13084,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>804</v>
       </c>
@@ -13092,7 +13095,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>807</v>
       </c>
@@ -13103,7 +13106,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>810</v>
       </c>
@@ -13114,7 +13117,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>813</v>
       </c>
@@ -13125,7 +13128,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>816</v>
       </c>
@@ -13136,7 +13139,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>819</v>
       </c>
@@ -13147,7 +13150,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>822</v>
       </c>
@@ -13158,7 +13161,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>825</v>
       </c>
@@ -13169,7 +13172,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>828</v>
       </c>
@@ -13180,7 +13183,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>831</v>
       </c>
@@ -13191,7 +13194,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>834</v>
       </c>
@@ -13202,7 +13205,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>837</v>
       </c>
@@ -13213,7 +13216,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>840</v>
       </c>
@@ -13224,7 +13227,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>843</v>
       </c>
@@ -13235,7 +13238,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>846</v>
       </c>
@@ -13246,7 +13249,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>849</v>
       </c>
@@ -13257,7 +13260,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>852</v>
       </c>
@@ -13268,7 +13271,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>855</v>
       </c>
@@ -13279,7 +13282,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>858</v>
       </c>
@@ -13290,7 +13293,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>861</v>
       </c>
@@ -13301,7 +13304,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>864</v>
       </c>
@@ -13312,7 +13315,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>867</v>
       </c>
@@ -13323,7 +13326,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>870</v>
       </c>
@@ -13334,7 +13337,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>873</v>
       </c>
@@ -13345,7 +13348,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>876</v>
       </c>
@@ -13356,7 +13359,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>879</v>
       </c>
@@ -13367,7 +13370,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>882</v>
       </c>
@@ -13378,7 +13381,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>885</v>
       </c>
@@ -13389,7 +13392,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>888</v>
       </c>
@@ -13400,7 +13403,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>891</v>
       </c>
@@ -13411,7 +13414,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>894</v>
       </c>
@@ -13422,7 +13425,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>897</v>
       </c>
@@ -13433,7 +13436,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>900</v>
       </c>
@@ -13444,7 +13447,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>903</v>
       </c>
@@ -13455,7 +13458,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>906</v>
       </c>
@@ -13466,7 +13469,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>909</v>
       </c>
@@ -13477,7 +13480,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>912</v>
       </c>
@@ -13488,7 +13491,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>915</v>
       </c>
@@ -13499,7 +13502,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>918</v>
       </c>
@@ -13510,7 +13513,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>921</v>
       </c>
@@ -13521,7 +13524,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>924</v>
       </c>
@@ -13532,7 +13535,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>927</v>
       </c>
@@ -13543,7 +13546,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>930</v>
       </c>
@@ -13554,7 +13557,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>933</v>
       </c>
@@ -13565,7 +13568,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>936</v>
       </c>
@@ -13576,7 +13579,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>939</v>
       </c>
@@ -13587,7 +13590,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>942</v>
       </c>
@@ -13598,7 +13601,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>945</v>
       </c>
@@ -13609,7 +13612,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>948</v>
       </c>
@@ -13620,7 +13623,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>951</v>
       </c>
@@ -13631,7 +13634,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>954</v>
       </c>
@@ -13642,7 +13645,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>957</v>
       </c>
@@ -13653,7 +13656,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>960</v>
       </c>
@@ -13664,7 +13667,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>963</v>
       </c>
@@ -13675,7 +13678,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>966</v>
       </c>
@@ -13686,7 +13689,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>969</v>
       </c>
@@ -13697,7 +13700,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>972</v>
       </c>
@@ -13708,7 +13711,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>975</v>
       </c>
@@ -13719,7 +13722,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>978</v>
       </c>
@@ -13730,7 +13733,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>981</v>
       </c>
@@ -13741,7 +13744,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>984</v>
       </c>
@@ -13752,7 +13755,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>987</v>
       </c>
@@ -13763,7 +13766,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>990</v>
       </c>
@@ -13774,7 +13777,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>993</v>
       </c>
@@ -13785,7 +13788,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>996</v>
       </c>
@@ -13796,7 +13799,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>999</v>
       </c>
@@ -13807,7 +13810,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1002</v>
       </c>
@@ -13818,7 +13821,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1005</v>
       </c>
@@ -13829,7 +13832,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1008</v>
       </c>
@@ -13840,7 +13843,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1011</v>
       </c>
@@ -13851,7 +13854,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1014</v>
       </c>
@@ -13862,7 +13865,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1017</v>
       </c>
@@ -13873,7 +13876,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1020</v>
       </c>
@@ -13884,7 +13887,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1023</v>
       </c>
@@ -13895,7 +13898,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1026</v>
       </c>
@@ -13906,7 +13909,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1029</v>
       </c>
@@ -13917,7 +13920,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1032</v>
       </c>
@@ -13928,7 +13931,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1035</v>
       </c>
@@ -13939,7 +13942,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1038</v>
       </c>
@@ -13950,7 +13953,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1041</v>
       </c>
@@ -13961,7 +13964,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1044</v>
       </c>
@@ -13972,7 +13975,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1047</v>
       </c>
@@ -13983,7 +13986,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1050</v>
       </c>
@@ -13994,7 +13997,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1053</v>
       </c>
@@ -14005,7 +14008,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1056</v>
       </c>
@@ -14016,7 +14019,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>1059</v>
       </c>
@@ -14027,7 +14030,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1062</v>
       </c>
@@ -14038,7 +14041,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1065</v>
       </c>
@@ -14049,7 +14052,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1068</v>
       </c>
@@ -14060,7 +14063,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1071</v>
       </c>
@@ -14071,7 +14074,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1074</v>
       </c>
@@ -14082,7 +14085,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1077</v>
       </c>
@@ -14093,7 +14096,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1080</v>
       </c>
@@ -14104,7 +14107,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1083</v>
       </c>
@@ -14115,7 +14118,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1086</v>
       </c>
@@ -14126,7 +14129,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1089</v>
       </c>
@@ -14137,7 +14140,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1092</v>
       </c>
@@ -14148,7 +14151,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1095</v>
       </c>
@@ -14159,7 +14162,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1098</v>
       </c>
@@ -14170,7 +14173,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>1101</v>
       </c>
@@ -14181,7 +14184,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>1104</v>
       </c>
@@ -14192,7 +14195,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>1107</v>
       </c>
@@ -14203,7 +14206,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>1110</v>
       </c>
@@ -14214,7 +14217,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>1113</v>
       </c>
@@ -14225,7 +14228,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>1116</v>
       </c>
@@ -14236,7 +14239,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>1119</v>
       </c>
@@ -14247,7 +14250,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>1122</v>
       </c>
@@ -14258,7 +14261,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>1125</v>
       </c>
@@ -14269,7 +14272,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>1128</v>
       </c>
@@ -14280,7 +14283,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>1131</v>
       </c>
@@ -14291,7 +14294,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>1134</v>
       </c>
@@ -14302,7 +14305,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>1137</v>
       </c>
@@ -14313,7 +14316,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>1140</v>
       </c>
@@ -14324,7 +14327,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>1143</v>
       </c>
@@ -14335,7 +14338,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>1146</v>
       </c>
@@ -14346,7 +14349,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>1149</v>
       </c>
@@ -14357,7 +14360,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>1152</v>
       </c>
@@ -14368,7 +14371,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>1155</v>
       </c>
@@ -14379,7 +14382,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>1158</v>
       </c>
@@ -14390,7 +14393,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>1161</v>
       </c>
@@ -14401,7 +14404,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>1164</v>
       </c>
@@ -14412,7 +14415,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>1167</v>
       </c>
@@ -14423,7 +14426,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>1170</v>
       </c>
@@ -14434,7 +14437,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>1173</v>
       </c>
@@ -14445,7 +14448,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>1176</v>
       </c>
@@ -14456,7 +14459,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>1179</v>
       </c>
@@ -14467,7 +14470,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>1182</v>
       </c>
@@ -14478,7 +14481,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>1185</v>
       </c>
@@ -14489,7 +14492,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>1188</v>
       </c>
@@ -14500,7 +14503,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>1191</v>
       </c>
@@ -14511,7 +14514,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>1194</v>
       </c>
@@ -14522,7 +14525,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>1197</v>
       </c>
@@ -14533,7 +14536,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>1200</v>
       </c>
@@ -14544,7 +14547,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>1203</v>
       </c>
@@ -14555,7 +14558,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>1206</v>
       </c>
@@ -14566,7 +14569,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>1209</v>
       </c>
@@ -14577,7 +14580,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>1212</v>
       </c>
@@ -14588,7 +14591,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>1215</v>
       </c>
@@ -14599,7 +14602,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>1218</v>
       </c>
@@ -14610,7 +14613,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>1221</v>
       </c>
@@ -14621,7 +14624,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>1224</v>
       </c>
@@ -14632,7 +14635,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>1227</v>
       </c>
@@ -14643,7 +14646,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>1230</v>
       </c>
@@ -14654,7 +14657,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>1233</v>
       </c>
@@ -14665,7 +14668,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1236</v>
       </c>
@@ -14676,7 +14679,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>1239</v>
       </c>
@@ -14687,7 +14690,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1242</v>
       </c>
@@ -14698,7 +14701,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1245</v>
       </c>
@@ -14709,7 +14712,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1248</v>
       </c>
@@ -14720,7 +14723,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>1251</v>
       </c>
@@ -14731,7 +14734,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1254</v>
       </c>
@@ -14742,7 +14745,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1257</v>
       </c>
@@ -14753,7 +14756,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>1260</v>
       </c>
@@ -14764,7 +14767,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1263</v>
       </c>
@@ -14775,7 +14778,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1266</v>
       </c>
@@ -14786,7 +14789,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1269</v>
       </c>
@@ -14797,7 +14800,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1272</v>
       </c>
@@ -14808,7 +14811,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1275</v>
       </c>
@@ -14819,7 +14822,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1278</v>
       </c>
@@ -14830,7 +14833,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1281</v>
       </c>
@@ -14841,7 +14844,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1284</v>
       </c>
@@ -14852,7 +14855,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1287</v>
       </c>
@@ -14863,7 +14866,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1290</v>
       </c>
@@ -14874,7 +14877,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1293</v>
       </c>
@@ -14885,7 +14888,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1296</v>
       </c>
@@ -14896,7 +14899,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1299</v>
       </c>
@@ -14907,7 +14910,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1302</v>
       </c>
@@ -14918,7 +14921,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1305</v>
       </c>
@@ -14929,7 +14932,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1308</v>
       </c>
@@ -14940,7 +14943,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1311</v>
       </c>
@@ -14951,7 +14954,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1314</v>
       </c>
@@ -14962,7 +14965,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1317</v>
       </c>
@@ -14973,7 +14976,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1320</v>
       </c>
@@ -14984,7 +14987,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1323</v>
       </c>
@@ -14995,7 +14998,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1326</v>
       </c>
@@ -15006,7 +15009,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1329</v>
       </c>
@@ -15017,7 +15020,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1332</v>
       </c>
@@ -15028,7 +15031,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1335</v>
       </c>
@@ -15039,7 +15042,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1338</v>
       </c>
@@ -15050,7 +15053,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1341</v>
       </c>
@@ -15061,7 +15064,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1344</v>
       </c>
@@ -15072,7 +15075,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1347</v>
       </c>
@@ -15083,7 +15086,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1350</v>
       </c>
@@ -15094,7 +15097,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1353</v>
       </c>
@@ -15105,7 +15108,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1356</v>
       </c>
@@ -15116,7 +15119,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1359</v>
       </c>
@@ -15127,7 +15130,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1362</v>
       </c>
@@ -15138,7 +15141,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1365</v>
       </c>
@@ -15149,7 +15152,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1368</v>
       </c>
@@ -15160,7 +15163,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1371</v>
       </c>
@@ -15171,7 +15174,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1374</v>
       </c>
@@ -15182,7 +15185,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1377</v>
       </c>
@@ -15193,7 +15196,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1380</v>
       </c>
@@ -15204,7 +15207,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1383</v>
       </c>
@@ -15215,7 +15218,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1386</v>
       </c>
@@ -15226,7 +15229,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>1389</v>
       </c>
@@ -15237,7 +15240,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>1392</v>
       </c>
@@ -15248,7 +15251,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>1395</v>
       </c>
@@ -15259,7 +15262,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>1398</v>
       </c>
@@ -15270,7 +15273,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>1401</v>
       </c>
@@ -15281,7 +15284,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>1404</v>
       </c>
@@ -15292,7 +15295,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>1407</v>
       </c>
@@ -15303,7 +15306,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1410</v>
       </c>
@@ -15314,7 +15317,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1413</v>
       </c>
@@ -15325,7 +15328,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1416</v>
       </c>
@@ -15336,7 +15339,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1419</v>
       </c>
@@ -15347,7 +15350,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>1422</v>
       </c>
@@ -15358,7 +15361,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>1425</v>
       </c>
@@ -15369,7 +15372,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>1428</v>
       </c>
@@ -15380,7 +15383,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>1431</v>
       </c>
@@ -15391,7 +15394,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>1434</v>
       </c>
@@ -15402,7 +15405,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>1437</v>
       </c>
@@ -15413,7 +15416,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>1440</v>
       </c>
@@ -15424,7 +15427,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>1443</v>
       </c>
@@ -15435,7 +15438,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>1446</v>
       </c>
@@ -15446,7 +15449,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>1449</v>
       </c>
@@ -15457,7 +15460,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>1452</v>
       </c>
@@ -15468,7 +15471,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>1455</v>
       </c>
@@ -15479,7 +15482,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>1458</v>
       </c>
@@ -15490,7 +15493,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>1461</v>
       </c>
@@ -15501,7 +15504,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>1464</v>
       </c>
@@ -15512,7 +15515,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>1467</v>
       </c>
@@ -15523,7 +15526,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>1470</v>
       </c>
@@ -15534,7 +15537,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>1473</v>
       </c>
@@ -15545,7 +15548,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>1476</v>
       </c>
@@ -15556,7 +15559,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>1479</v>
       </c>
@@ -15567,7 +15570,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>1482</v>
       </c>
@@ -15578,7 +15581,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>1485</v>
       </c>
@@ -15589,7 +15592,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>1488</v>
       </c>
@@ -15600,7 +15603,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>1491</v>
       </c>
@@ -15611,7 +15614,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>1494</v>
       </c>
@@ -15622,7 +15625,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>1497</v>
       </c>
@@ -15633,7 +15636,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>1500</v>
       </c>
@@ -15644,7 +15647,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>1269</v>
       </c>
@@ -15655,7 +15658,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>1505</v>
       </c>
@@ -15666,7 +15669,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>1508</v>
       </c>
@@ -15677,7 +15680,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>1511</v>
       </c>
@@ -15688,7 +15691,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>1514</v>
       </c>
@@ -15699,7 +15702,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>1517</v>
       </c>
@@ -15710,7 +15713,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>1520</v>
       </c>
@@ -15721,7 +15724,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>1523</v>
       </c>
@@ -15732,7 +15735,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>1526</v>
       </c>
@@ -15743,7 +15746,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>1529</v>
       </c>
@@ -15754,7 +15757,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>1532</v>
       </c>
@@ -15765,7 +15768,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>1535</v>
       </c>
@@ -15776,7 +15779,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>1538</v>
       </c>
@@ -15787,7 +15790,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>1541</v>
       </c>
@@ -15798,7 +15801,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>1544</v>
       </c>
@@ -15809,7 +15812,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>1547</v>
       </c>
@@ -15820,7 +15823,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>1550</v>
       </c>
@@ -15831,7 +15834,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>1553</v>
       </c>
@@ -15842,7 +15845,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>1556</v>
       </c>
@@ -15853,7 +15856,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>1559</v>
       </c>
@@ -15864,7 +15867,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>1562</v>
       </c>
@@ -15875,7 +15878,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>1565</v>
       </c>
@@ -15886,7 +15889,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>1568</v>
       </c>
@@ -15897,7 +15900,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>1571</v>
       </c>
@@ -15908,7 +15911,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>1574</v>
       </c>
@@ -15919,7 +15922,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>1577</v>
       </c>
@@ -15930,7 +15933,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>1580</v>
       </c>
@@ -15941,7 +15944,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>1583</v>
       </c>
@@ -15952,7 +15955,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>1586</v>
       </c>
@@ -15963,7 +15966,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>1589</v>
       </c>
@@ -15974,7 +15977,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>1592</v>
       </c>
@@ -15985,7 +15988,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>1595</v>
       </c>
@@ -15996,7 +15999,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>1598</v>
       </c>
@@ -16007,7 +16010,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>1601</v>
       </c>
@@ -16018,7 +16021,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>1604</v>
       </c>
@@ -16029,7 +16032,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>1607</v>
       </c>
@@ -16040,7 +16043,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>1610</v>
       </c>
@@ -16051,7 +16054,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>1613</v>
       </c>
@@ -16062,7 +16065,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>1616</v>
       </c>
@@ -16073,7 +16076,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>1619</v>
       </c>
@@ -16084,7 +16087,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>1622</v>
       </c>
@@ -16095,7 +16098,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>1625</v>
       </c>
@@ -16106,7 +16109,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>1628</v>
       </c>
@@ -16117,7 +16120,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>1631</v>
       </c>
@@ -16128,7 +16131,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>1634</v>
       </c>
@@ -16139,7 +16142,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>1637</v>
       </c>
@@ -16150,7 +16153,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>1640</v>
       </c>
@@ -16161,7 +16164,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>1643</v>
       </c>
@@ -16172,7 +16175,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>1646</v>
       </c>
@@ -16183,7 +16186,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>1649</v>
       </c>
@@ -16194,7 +16197,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>1652</v>
       </c>
@@ -16205,7 +16208,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>1655</v>
       </c>
@@ -16216,7 +16219,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>1658</v>
       </c>
@@ -16227,7 +16230,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>1661</v>
       </c>
@@ -16238,7 +16241,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>1664</v>
       </c>
@@ -16249,7 +16252,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>1667</v>
       </c>
@@ -16260,7 +16263,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>1670</v>
       </c>
@@ -16271,7 +16274,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>1673</v>
       </c>
@@ -16282,7 +16285,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>1676</v>
       </c>
@@ -16293,7 +16296,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>1679</v>
       </c>
@@ -16304,7 +16307,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>1682</v>
       </c>
@@ -16315,7 +16318,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>1685</v>
       </c>
@@ -16326,7 +16329,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>1688</v>
       </c>
@@ -16337,7 +16340,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>1691</v>
       </c>
@@ -16348,7 +16351,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>1694</v>
       </c>
@@ -16359,7 +16362,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>1697</v>
       </c>
@@ -16370,7 +16373,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>1700</v>
       </c>
@@ -16381,7 +16384,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>1703</v>
       </c>
@@ -16392,7 +16395,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>1706</v>
       </c>
@@ -16403,7 +16406,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>1709</v>
       </c>
@@ -16414,7 +16417,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>1712</v>
       </c>
@@ -16425,7 +16428,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>1715</v>
       </c>
@@ -16436,7 +16439,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>1718</v>
       </c>
@@ -16447,7 +16450,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>1721</v>
       </c>
@@ -16458,7 +16461,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>1724</v>
       </c>
@@ -16469,7 +16472,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>1727</v>
       </c>
@@ -16480,7 +16483,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>1730</v>
       </c>
@@ -16491,7 +16494,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>1733</v>
       </c>
@@ -16502,7 +16505,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>1736</v>
       </c>
@@ -16513,7 +16516,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>1739</v>
       </c>
@@ -16524,7 +16527,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>1742</v>
       </c>
@@ -16535,7 +16538,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>1745</v>
       </c>
@@ -16546,7 +16549,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>1748</v>
       </c>
@@ -16557,7 +16560,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>1751</v>
       </c>
@@ -16568,7 +16571,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>1754</v>
       </c>
@@ -16579,7 +16582,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>1757</v>
       </c>
@@ -16590,7 +16593,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>1760</v>
       </c>
@@ -16601,7 +16604,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>1763</v>
       </c>
@@ -16612,7 +16615,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>1766</v>
       </c>
@@ -16623,7 +16626,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>1769</v>
       </c>
@@ -16634,7 +16637,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>1772</v>
       </c>
@@ -16645,7 +16648,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>1775</v>
       </c>
@@ -16656,7 +16659,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>1778</v>
       </c>
@@ -16667,7 +16670,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>1781</v>
       </c>
@@ -16678,7 +16681,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>1784</v>
       </c>
@@ -16689,7 +16692,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>1787</v>
       </c>
@@ -16700,7 +16703,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>1790</v>
       </c>
@@ -16711,7 +16714,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>1793</v>
       </c>
@@ -16722,7 +16725,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>1796</v>
       </c>
@@ -16733,7 +16736,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>1799</v>
       </c>
@@ -16744,7 +16747,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>1802</v>
       </c>
@@ -16755,7 +16758,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>1805</v>
       </c>
@@ -16766,7 +16769,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>1808</v>
       </c>
@@ -16777,7 +16780,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>1811</v>
       </c>
@@ -16788,7 +16791,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>1814</v>
       </c>
@@ -16799,7 +16802,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>1817</v>
       </c>
@@ -16810,7 +16813,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>1820</v>
       </c>
@@ -16821,7 +16824,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>1823</v>
       </c>
@@ -16832,7 +16835,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>1826</v>
       </c>
@@ -16843,7 +16846,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>1829</v>
       </c>
@@ -16854,7 +16857,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>1832</v>
       </c>
@@ -16865,7 +16868,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>1835</v>
       </c>
@@ -16876,7 +16879,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>1838</v>
       </c>
@@ -16887,7 +16890,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>1841</v>
       </c>
@@ -16898,7 +16901,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>1844</v>
       </c>
@@ -16909,7 +16912,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>1847</v>
       </c>
@@ -16920,7 +16923,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>1850</v>
       </c>
@@ -16931,7 +16934,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>1853</v>
       </c>
@@ -16942,7 +16945,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>1856</v>
       </c>
@@ -16953,7 +16956,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>1859</v>
       </c>
@@ -16964,7 +16967,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>1862</v>
       </c>
@@ -16975,7 +16978,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>1865</v>
       </c>
@@ -16986,7 +16989,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>1868</v>
       </c>
@@ -16997,7 +17000,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>1871</v>
       </c>
@@ -17008,7 +17011,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>1874</v>
       </c>
@@ -17019,7 +17022,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>1877</v>
       </c>
@@ -17030,7 +17033,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>1880</v>
       </c>
@@ -17041,7 +17044,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>1883</v>
       </c>
@@ -17052,7 +17055,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>1886</v>
       </c>
@@ -17063,7 +17066,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>1889</v>
       </c>
@@ -17074,7 +17077,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>1892</v>
       </c>
@@ -17085,7 +17088,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>1895</v>
       </c>
@@ -17096,7 +17099,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>1898</v>
       </c>
@@ -17107,7 +17110,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>1901</v>
       </c>
@@ -17118,7 +17121,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>1904</v>
       </c>
@@ -17129,7 +17132,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>1907</v>
       </c>
@@ -17140,7 +17143,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>1910</v>
       </c>
@@ -17151,7 +17154,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>1913</v>
       </c>
@@ -17162,7 +17165,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>1916</v>
       </c>
@@ -17173,7 +17176,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>1919</v>
       </c>
@@ -17184,7 +17187,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>1922</v>
       </c>
@@ -17195,7 +17198,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>1925</v>
       </c>
@@ -17206,7 +17209,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>1928</v>
       </c>
@@ -17217,7 +17220,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>1931</v>
       </c>
@@ -17228,7 +17231,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>1934</v>
       </c>
@@ -17239,7 +17242,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>1937</v>
       </c>
@@ -17250,7 +17253,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>1940</v>
       </c>
@@ -17261,7 +17264,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>1943</v>
       </c>
@@ -17272,7 +17275,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>1946</v>
       </c>
@@ -17283,7 +17286,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>1949</v>
       </c>
@@ -17294,7 +17297,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>1952</v>
       </c>
@@ -17305,7 +17308,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>1955</v>
       </c>
@@ -17316,7 +17319,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>1958</v>
       </c>
@@ -17327,7 +17330,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>1961</v>
       </c>
@@ -17338,7 +17341,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>1964</v>
       </c>
@@ -17349,7 +17352,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>1967</v>
       </c>
@@ -17360,7 +17363,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>1970</v>
       </c>
@@ -17371,7 +17374,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>1973</v>
       </c>
@@ -17382,7 +17385,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>1976</v>
       </c>
@@ -17393,7 +17396,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>1979</v>
       </c>
@@ -17404,7 +17407,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>1982</v>
       </c>
@@ -17415,7 +17418,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>1985</v>
       </c>
@@ -17426,7 +17429,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>1988</v>
       </c>
@@ -17437,7 +17440,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>1991</v>
       </c>
@@ -17448,7 +17451,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>1994</v>
       </c>
@@ -17459,7 +17462,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>1997</v>
       </c>
@@ -17470,7 +17473,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>2000</v>
       </c>
@@ -17481,7 +17484,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>2003</v>
       </c>
@@ -17492,7 +17495,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>2006</v>
       </c>
@@ -17503,7 +17506,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>2009</v>
       </c>
@@ -17514,7 +17517,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>2012</v>
       </c>
@@ -17525,7 +17528,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>2015</v>
       </c>
@@ -17536,7 +17539,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>2018</v>
       </c>
@@ -17547,7 +17550,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>2021</v>
       </c>
@@ -17558,7 +17561,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>2024</v>
       </c>
@@ -17569,7 +17572,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>2027</v>
       </c>
@@ -17580,7 +17583,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>2030</v>
       </c>
@@ -17591,7 +17594,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>2033</v>
       </c>
@@ -17602,7 +17605,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>2036</v>
       </c>
@@ -17613,7 +17616,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>2039</v>
       </c>
@@ -17624,7 +17627,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>2042</v>
       </c>
@@ -17635,7 +17638,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>2045</v>
       </c>
@@ -17646,7 +17649,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>2048</v>
       </c>
@@ -17657,7 +17660,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>2051</v>
       </c>
@@ -17668,7 +17671,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>2054</v>
       </c>
@@ -17679,7 +17682,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>2057</v>
       </c>
@@ -17690,7 +17693,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>2060</v>
       </c>
@@ -17701,7 +17704,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>2063</v>
       </c>
@@ -17712,7 +17715,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>2066</v>
       </c>
@@ -17723,7 +17726,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>2069</v>
       </c>
@@ -17734,7 +17737,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>2072</v>
       </c>
@@ -17745,7 +17748,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>2075</v>
       </c>
@@ -17756,7 +17759,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>2078</v>
       </c>
@@ -17767,7 +17770,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>2081</v>
       </c>
@@ -17778,7 +17781,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>2084</v>
       </c>
@@ -17789,7 +17792,7 @@
         <v>2086</v>
       </c>
     </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>2087</v>
       </c>
@@ -17800,7 +17803,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>2090</v>
       </c>
@@ -17811,7 +17814,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>2093</v>
       </c>
@@ -17822,7 +17825,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>2096</v>
       </c>
@@ -17833,7 +17836,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>2099</v>
       </c>
@@ -17844,7 +17847,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>2102</v>
       </c>
@@ -17855,7 +17858,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>2105</v>
       </c>
@@ -17866,7 +17869,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>2108</v>
       </c>
@@ -17877,7 +17880,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>2111</v>
       </c>
@@ -17888,7 +17891,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>2114</v>
       </c>
@@ -17899,7 +17902,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>2117</v>
       </c>
@@ -17910,7 +17913,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>2120</v>
       </c>
@@ -17921,7 +17924,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>2123</v>
       </c>
@@ -17932,7 +17935,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>2126</v>
       </c>
@@ -17943,7 +17946,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>2129</v>
       </c>
@@ -17954,7 +17957,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>2132</v>
       </c>
@@ -17965,7 +17968,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>2135</v>
       </c>
@@ -17976,7 +17979,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>2138</v>
       </c>
@@ -17987,7 +17990,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>2141</v>
       </c>
@@ -17998,7 +18001,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>2144</v>
       </c>
@@ -18009,7 +18012,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>2147</v>
       </c>
@@ -18020,7 +18023,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>2150</v>
       </c>
@@ -18031,7 +18034,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>2153</v>
       </c>
@@ -18042,7 +18045,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>2156</v>
       </c>
@@ -18053,7 +18056,7 @@
         <v>2158</v>
       </c>
     </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>2159</v>
       </c>
@@ -18064,7 +18067,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>2162</v>
       </c>
@@ -18075,7 +18078,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>2165</v>
       </c>
@@ -18086,7 +18089,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>2168</v>
       </c>
@@ -18097,7 +18100,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>2171</v>
       </c>
@@ -18108,7 +18111,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>2174</v>
       </c>
@@ -18119,7 +18122,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>2177</v>
       </c>
@@ -18130,7 +18133,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>2180</v>
       </c>
@@ -18141,7 +18144,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>2183</v>
       </c>
@@ -18152,7 +18155,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>2186</v>
       </c>
@@ -18163,7 +18166,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>2189</v>
       </c>
@@ -18174,7 +18177,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>2192</v>
       </c>
@@ -18185,7 +18188,7 @@
         <v>3256</v>
       </c>
     </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>2194</v>
       </c>
@@ -18196,7 +18199,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>2197</v>
       </c>
@@ -18207,7 +18210,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>2200</v>
       </c>
@@ -18218,7 +18221,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>2203</v>
       </c>
@@ -18229,7 +18232,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>2206</v>
       </c>
@@ -18240,7 +18243,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>2209</v>
       </c>
@@ -18251,7 +18254,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>2212</v>
       </c>
@@ -18262,7 +18265,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>2215</v>
       </c>
@@ -18273,7 +18276,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>2218</v>
       </c>
@@ -18284,7 +18287,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>2221</v>
       </c>
@@ -18295,7 +18298,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>2224</v>
       </c>
@@ -18306,7 +18309,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>2227</v>
       </c>
@@ -18317,7 +18320,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>2230</v>
       </c>
@@ -18328,7 +18331,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>2233</v>
       </c>
@@ -18339,7 +18342,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>2236</v>
       </c>
@@ -18350,7 +18353,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>2239</v>
       </c>
@@ -18361,7 +18364,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>2242</v>
       </c>
@@ -18372,7 +18375,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>2245</v>
       </c>
@@ -18383,7 +18386,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>2248</v>
       </c>
@@ -18394,7 +18397,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>2251</v>
       </c>
@@ -18405,7 +18408,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>2254</v>
       </c>
@@ -18416,7 +18419,7 @@
         <v>2256</v>
       </c>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>2257</v>
       </c>
@@ -18427,7 +18430,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>2260</v>
       </c>
@@ -18438,7 +18441,7 @@
         <v>2262</v>
       </c>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>2263</v>
       </c>
@@ -18449,7 +18452,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>2266</v>
       </c>
@@ -18460,7 +18463,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>2269</v>
       </c>
@@ -18471,7 +18474,7 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>2272</v>
       </c>
@@ -18482,7 +18485,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>2275</v>
       </c>
@@ -18493,7 +18496,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>2278</v>
       </c>
@@ -18504,7 +18507,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>2281</v>
       </c>
@@ -18515,7 +18518,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>2284</v>
       </c>
@@ -18526,7 +18529,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>2287</v>
       </c>
@@ -18537,7 +18540,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>2290</v>
       </c>
@@ -18548,7 +18551,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>2293</v>
       </c>
@@ -18559,7 +18562,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>2296</v>
       </c>
@@ -18570,7 +18573,7 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>2299</v>
       </c>
@@ -18581,7 +18584,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>2302</v>
       </c>
@@ -18592,7 +18595,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>2305</v>
       </c>
@@ -18603,7 +18606,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>2308</v>
       </c>
@@ -18614,7 +18617,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>2311</v>
       </c>
@@ -18625,7 +18628,7 @@
         <v>2313</v>
       </c>
     </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>2314</v>
       </c>
@@ -18636,7 +18639,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>2317</v>
       </c>
@@ -18647,7 +18650,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>2320</v>
       </c>
@@ -18658,7 +18661,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>2323</v>
       </c>
@@ -18669,7 +18672,7 @@
         <v>2325</v>
       </c>
     </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>2326</v>
       </c>
@@ -18680,7 +18683,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>2329</v>
       </c>
@@ -18691,7 +18694,7 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>2332</v>
       </c>
@@ -18702,7 +18705,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>2335</v>
       </c>
@@ -18713,7 +18716,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>2338</v>
       </c>
@@ -18724,7 +18727,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>2341</v>
       </c>
@@ -18735,7 +18738,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>2344</v>
       </c>
@@ -18746,7 +18749,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>2347</v>
       </c>
@@ -18757,7 +18760,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>2350</v>
       </c>
@@ -18768,7 +18771,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>2353</v>
       </c>
@@ -18779,7 +18782,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>2356</v>
       </c>
@@ -18790,7 +18793,7 @@
         <v>2358</v>
       </c>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>2359</v>
       </c>
@@ -18801,7 +18804,7 @@
         <v>2361</v>
       </c>
     </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>2362</v>
       </c>
@@ -18812,7 +18815,7 @@
         <v>2364</v>
       </c>
     </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>2365</v>
       </c>
@@ -18823,7 +18826,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>2368</v>
       </c>
@@ -18834,7 +18837,7 @@
         <v>2370</v>
       </c>
     </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>2371</v>
       </c>
@@ -18845,7 +18848,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>2374</v>
       </c>
@@ -18856,7 +18859,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>2377</v>
       </c>
@@ -18867,7 +18870,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>2380</v>
       </c>
@@ -18878,7 +18881,7 @@
         <v>2382</v>
       </c>
     </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>2383</v>
       </c>
@@ -18889,7 +18892,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>2386</v>
       </c>
@@ -18900,7 +18903,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>2389</v>
       </c>
@@ -18911,7 +18914,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>2392</v>
       </c>
@@ -18922,7 +18925,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>2395</v>
       </c>
@@ -18933,7 +18936,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>2398</v>
       </c>
@@ -18944,7 +18947,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>2401</v>
       </c>
@@ -18955,7 +18958,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>2404</v>
       </c>
@@ -18966,7 +18969,7 @@
         <v>2406</v>
       </c>
     </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>2407</v>
       </c>
@@ -18977,7 +18980,7 @@
         <v>2409</v>
       </c>
     </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>2410</v>
       </c>
@@ -18988,7 +18991,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>2413</v>
       </c>
@@ -18999,7 +19002,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>2416</v>
       </c>
@@ -19010,7 +19013,7 @@
         <v>2418</v>
       </c>
     </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>2419</v>
       </c>
@@ -19021,7 +19024,7 @@
         <v>2421</v>
       </c>
     </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>2422</v>
       </c>
@@ -19032,7 +19035,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>2425</v>
       </c>
@@ -19043,7 +19046,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>2428</v>
       </c>
@@ -19054,7 +19057,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>2431</v>
       </c>
@@ -19065,7 +19068,7 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>2434</v>
       </c>
@@ -19076,7 +19079,7 @@
         <v>2436</v>
       </c>
     </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>2437</v>
       </c>
@@ -19087,7 +19090,7 @@
         <v>2439</v>
       </c>
     </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>2440</v>
       </c>
@@ -19098,7 +19101,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>2443</v>
       </c>
@@ -19109,7 +19112,7 @@
         <v>2445</v>
       </c>
     </row>
-    <row r="817" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>2446</v>
       </c>
@@ -19120,7 +19123,7 @@
         <v>2448</v>
       </c>
     </row>
-    <row r="818" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>2449</v>
       </c>
@@ -19131,7 +19134,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="819" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>2452</v>
       </c>
@@ -19142,7 +19145,7 @@
         <v>2454</v>
       </c>
     </row>
-    <row r="820" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>2455</v>
       </c>
@@ -19153,7 +19156,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="821" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>2458</v>
       </c>
@@ -19164,7 +19167,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="822" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>2461</v>
       </c>
@@ -19175,7 +19178,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="823" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>2464</v>
       </c>
@@ -19186,7 +19189,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="824" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>2467</v>
       </c>
@@ -19197,7 +19200,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="825" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>2470</v>
       </c>
@@ -19208,7 +19211,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="826" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>2473</v>
       </c>
@@ -19219,7 +19222,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="827" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>2476</v>
       </c>
@@ -19230,7 +19233,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="828" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>2479</v>
       </c>
@@ -19241,7 +19244,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="829" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>2482</v>
       </c>
@@ -19252,7 +19255,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="830" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>2485</v>
       </c>
@@ -19263,7 +19266,7 @@
         <v>2487</v>
       </c>
     </row>
-    <row r="831" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>2488</v>
       </c>
@@ -19274,7 +19277,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="832" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>2491</v>
       </c>
@@ -19285,7 +19288,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="833" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>2494</v>
       </c>
@@ -19296,7 +19299,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="834" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>2497</v>
       </c>
@@ -19307,7 +19310,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="835" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>2500</v>
       </c>
@@ -19318,7 +19321,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="836" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>2503</v>
       </c>
@@ -19329,7 +19332,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="837" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>2506</v>
       </c>
@@ -19340,7 +19343,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="838" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>2509</v>
       </c>
@@ -19351,7 +19354,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="839" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>2512</v>
       </c>
@@ -19362,7 +19365,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="840" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>2515</v>
       </c>
@@ -19373,7 +19376,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="841" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>2518</v>
       </c>
@@ -19384,7 +19387,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="842" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>2521</v>
       </c>
@@ -19395,7 +19398,7 @@
         <v>2523</v>
       </c>
     </row>
-    <row r="843" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>2524</v>
       </c>
@@ -19406,7 +19409,7 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="844" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>2527</v>
       </c>
@@ -19417,7 +19420,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="845" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>2530</v>
       </c>
@@ -19428,7 +19431,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="846" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>2533</v>
       </c>
@@ -19439,7 +19442,7 @@
         <v>2535</v>
       </c>
     </row>
-    <row r="847" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>2536</v>
       </c>
@@ -19450,7 +19453,7 @@
         <v>2538</v>
       </c>
     </row>
-    <row r="848" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>2539</v>
       </c>
@@ -19461,7 +19464,7 @@
         <v>2541</v>
       </c>
     </row>
-    <row r="849" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>2542</v>
       </c>
@@ -19472,7 +19475,7 @@
         <v>2544</v>
       </c>
     </row>
-    <row r="850" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>2545</v>
       </c>
@@ -19483,7 +19486,7 @@
         <v>2547</v>
       </c>
     </row>
-    <row r="851" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
         <v>2548</v>
       </c>
@@ -19494,7 +19497,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="852" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>2551</v>
       </c>
@@ -19505,7 +19508,7 @@
         <v>2553</v>
       </c>
     </row>
-    <row r="853" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
         <v>2554</v>
       </c>
@@ -19516,7 +19519,7 @@
         <v>2556</v>
       </c>
     </row>
-    <row r="854" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>2557</v>
       </c>
@@ -19527,7 +19530,7 @@
         <v>2559</v>
       </c>
     </row>
-    <row r="855" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>2560</v>
       </c>
@@ -19538,7 +19541,7 @@
         <v>2562</v>
       </c>
     </row>
-    <row r="856" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>2563</v>
       </c>
@@ -19549,7 +19552,7 @@
         <v>2565</v>
       </c>
     </row>
-    <row r="857" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>2566</v>
       </c>
@@ -19560,7 +19563,7 @@
         <v>2568</v>
       </c>
     </row>
-    <row r="858" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
         <v>2569</v>
       </c>
@@ -19571,7 +19574,7 @@
         <v>2571</v>
       </c>
     </row>
-    <row r="859" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>2572</v>
       </c>
@@ -19582,7 +19585,7 @@
         <v>2574</v>
       </c>
     </row>
-    <row r="860" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>2575</v>
       </c>
@@ -19593,7 +19596,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="861" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>2578</v>
       </c>
@@ -19604,7 +19607,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="862" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>2581</v>
       </c>
@@ -19615,7 +19618,7 @@
         <v>2583</v>
       </c>
     </row>
-    <row r="863" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
         <v>2584</v>
       </c>
@@ -19626,7 +19629,7 @@
         <v>2586</v>
       </c>
     </row>
-    <row r="864" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
         <v>2587</v>
       </c>
@@ -19637,7 +19640,7 @@
         <v>2589</v>
       </c>
     </row>
-    <row r="865" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
         <v>2590</v>
       </c>
@@ -19648,7 +19651,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="866" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
         <v>2593</v>
       </c>
@@ -19659,7 +19662,7 @@
         <v>2595</v>
       </c>
     </row>
-    <row r="867" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
         <v>2596</v>
       </c>
@@ -19670,7 +19673,7 @@
         <v>2598</v>
       </c>
     </row>
-    <row r="868" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
         <v>2599</v>
       </c>
@@ -19681,7 +19684,7 @@
         <v>2601</v>
       </c>
     </row>
-    <row r="869" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
         <v>2602</v>
       </c>
@@ -19692,7 +19695,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="870" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
         <v>2605</v>
       </c>
@@ -19703,7 +19706,7 @@
         <v>2607</v>
       </c>
     </row>
-    <row r="871" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
         <v>2608</v>
       </c>
@@ -19714,7 +19717,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="872" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
         <v>2611</v>
       </c>
@@ -19725,7 +19728,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="873" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
         <v>2614</v>
       </c>
@@ -19736,7 +19739,7 @@
         <v>2616</v>
       </c>
     </row>
-    <row r="874" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
         <v>2617</v>
       </c>
@@ -19747,7 +19750,7 @@
         <v>2619</v>
       </c>
     </row>
-    <row r="875" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
         <v>2620</v>
       </c>
@@ -19758,7 +19761,7 @@
         <v>2622</v>
       </c>
     </row>
-    <row r="876" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
         <v>2623</v>
       </c>
@@ -19769,7 +19772,7 @@
         <v>2625</v>
       </c>
     </row>
-    <row r="877" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
         <v>2626</v>
       </c>
@@ -19780,7 +19783,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="878" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
         <v>2629</v>
       </c>
@@ -19791,7 +19794,7 @@
         <v>2631</v>
       </c>
     </row>
-    <row r="879" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
         <v>2632</v>
       </c>
@@ -19802,7 +19805,7 @@
         <v>2634</v>
       </c>
     </row>
-    <row r="880" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
         <v>2635</v>
       </c>
@@ -19813,7 +19816,7 @@
         <v>2637</v>
       </c>
     </row>
-    <row r="881" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
         <v>2638</v>
       </c>
@@ -19824,7 +19827,7 @@
         <v>2640</v>
       </c>
     </row>
-    <row r="882" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
         <v>2641</v>
       </c>
@@ -19835,7 +19838,7 @@
         <v>2643</v>
       </c>
     </row>
-    <row r="883" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
         <v>2644</v>
       </c>
@@ -19846,7 +19849,7 @@
         <v>2646</v>
       </c>
     </row>
-    <row r="884" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
         <v>2647</v>
       </c>
@@ -19857,7 +19860,7 @@
         <v>2649</v>
       </c>
     </row>
-    <row r="885" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
         <v>2650</v>
       </c>
@@ -19868,7 +19871,7 @@
         <v>2652</v>
       </c>
     </row>
-    <row r="886" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
         <v>2653</v>
       </c>
@@ -19879,7 +19882,7 @@
         <v>2655</v>
       </c>
     </row>
-    <row r="887" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
         <v>2656</v>
       </c>
@@ -19890,7 +19893,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="888" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
         <v>2659</v>
       </c>
@@ -19901,7 +19904,7 @@
         <v>2661</v>
       </c>
     </row>
-    <row r="889" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
         <v>2662</v>
       </c>
@@ -19912,7 +19915,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="890" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
         <v>2665</v>
       </c>
@@ -19923,7 +19926,7 @@
         <v>2667</v>
       </c>
     </row>
-    <row r="891" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
         <v>2668</v>
       </c>
@@ -19934,7 +19937,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="892" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
         <v>2671</v>
       </c>
@@ -19945,7 +19948,7 @@
         <v>2673</v>
       </c>
     </row>
-    <row r="893" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
         <v>2674</v>
       </c>
@@ -19956,7 +19959,7 @@
         <v>2676</v>
       </c>
     </row>
-    <row r="894" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
         <v>2677</v>
       </c>
@@ -19967,7 +19970,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="895" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
         <v>2680</v>
       </c>
@@ -19978,7 +19981,7 @@
         <v>2682</v>
       </c>
     </row>
-    <row r="896" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
         <v>2683</v>
       </c>
@@ -19989,7 +19992,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="897" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>2686</v>
       </c>
@@ -20000,7 +20003,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="898" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>2689</v>
       </c>
@@ -20011,7 +20014,7 @@
         <v>2691</v>
       </c>
     </row>
-    <row r="899" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>2692</v>
       </c>
@@ -20022,7 +20025,7 @@
         <v>2694</v>
       </c>
     </row>
-    <row r="900" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>2695</v>
       </c>
@@ -20033,7 +20036,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="901" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>2698</v>
       </c>
@@ -20044,7 +20047,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="902" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>2701</v>
       </c>
@@ -20055,7 +20058,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="903" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>2704</v>
       </c>
@@ -20066,7 +20069,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="904" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>2707</v>
       </c>
@@ -20077,7 +20080,7 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="905" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
         <v>2710</v>
       </c>
@@ -20088,7 +20091,7 @@
         <v>2712</v>
       </c>
     </row>
-    <row r="906" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
         <v>2713</v>
       </c>
@@ -20099,7 +20102,7 @@
         <v>2715</v>
       </c>
     </row>
-    <row r="907" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
         <v>2716</v>
       </c>
@@ -20110,7 +20113,7 @@
         <v>2718</v>
       </c>
     </row>
-    <row r="908" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
         <v>2719</v>
       </c>
@@ -20121,7 +20124,7 @@
         <v>2721</v>
       </c>
     </row>
-    <row r="909" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
         <v>2722</v>
       </c>
@@ -20132,7 +20135,7 @@
         <v>2724</v>
       </c>
     </row>
-    <row r="910" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
         <v>2725</v>
       </c>
@@ -20143,7 +20146,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="911" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
         <v>2728</v>
       </c>
@@ -20154,7 +20157,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="912" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
         <v>2731</v>
       </c>
@@ -20165,7 +20168,7 @@
         <v>2733</v>
       </c>
     </row>
-    <row r="913" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
         <v>2734</v>
       </c>
@@ -20176,7 +20179,7 @@
         <v>2736</v>
       </c>
     </row>
-    <row r="914" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A914" t="s">
         <v>2737</v>
       </c>
@@ -20187,7 +20190,7 @@
         <v>2739</v>
       </c>
     </row>
-    <row r="915" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A915" t="s">
         <v>2740</v>
       </c>
@@ -20198,7 +20201,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="916" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A916" t="s">
         <v>2743</v>
       </c>
@@ -20209,7 +20212,7 @@
         <v>2745</v>
       </c>
     </row>
-    <row r="917" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
         <v>2746</v>
       </c>
@@ -20220,7 +20223,7 @@
         <v>2748</v>
       </c>
     </row>
-    <row r="918" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A918" t="s">
         <v>2749</v>
       </c>
@@ -20231,7 +20234,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="919" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
         <v>2752</v>
       </c>
@@ -20242,7 +20245,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="920" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
         <v>2755</v>
       </c>
@@ -20253,7 +20256,7 @@
         <v>2757</v>
       </c>
     </row>
-    <row r="921" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
         <v>2758</v>
       </c>
@@ -20264,7 +20267,7 @@
         <v>2760</v>
       </c>
     </row>
-    <row r="922" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
         <v>2761</v>
       </c>
@@ -20275,7 +20278,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="923" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
         <v>2764</v>
       </c>
@@ -20286,7 +20289,7 @@
         <v>2766</v>
       </c>
     </row>
-    <row r="924" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
         <v>2767</v>
       </c>
@@ -20297,7 +20300,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="925" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
         <v>2770</v>
       </c>
@@ -20308,7 +20311,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="926" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
         <v>2773</v>
       </c>
@@ -20319,7 +20322,7 @@
         <v>2775</v>
       </c>
     </row>
-    <row r="927" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
         <v>2776</v>
       </c>
@@ -20330,7 +20333,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="928" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
         <v>2779</v>
       </c>
@@ -20341,7 +20344,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="929" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
         <v>2782</v>
       </c>
@@ -20352,7 +20355,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="930" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
         <v>2785</v>
       </c>
@@ -20363,7 +20366,7 @@
         <v>2787</v>
       </c>
     </row>
-    <row r="931" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
         <v>2788</v>
       </c>
@@ -20374,7 +20377,7 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="932" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
         <v>2791</v>
       </c>
@@ -20385,7 +20388,7 @@
         <v>2793</v>
       </c>
     </row>
-    <row r="933" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
         <v>2794</v>
       </c>
@@ -20396,7 +20399,7 @@
         <v>2796</v>
       </c>
     </row>
-    <row r="934" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
         <v>2797</v>
       </c>
@@ -20407,7 +20410,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="935" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
         <v>2800</v>
       </c>
@@ -20418,7 +20421,7 @@
         <v>2802</v>
       </c>
     </row>
-    <row r="936" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
         <v>2803</v>
       </c>
@@ -20429,7 +20432,7 @@
         <v>2805</v>
       </c>
     </row>
-    <row r="937" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
         <v>2806</v>
       </c>
@@ -20440,7 +20443,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="938" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
         <v>2809</v>
       </c>
@@ -20451,7 +20454,7 @@
         <v>2811</v>
       </c>
     </row>
-    <row r="939" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
         <v>2812</v>
       </c>
@@ -20462,7 +20465,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="940" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
         <v>2815</v>
       </c>
@@ -20473,7 +20476,7 @@
         <v>2817</v>
       </c>
     </row>
-    <row r="941" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
         <v>2818</v>
       </c>
@@ -20484,7 +20487,7 @@
         <v>2820</v>
       </c>
     </row>
-    <row r="942" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
         <v>2821</v>
       </c>
@@ -20495,7 +20498,7 @@
         <v>2823</v>
       </c>
     </row>
-    <row r="943" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
         <v>2824</v>
       </c>
@@ -20506,7 +20509,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="944" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
         <v>2827</v>
       </c>
@@ -20517,7 +20520,7 @@
         <v>2829</v>
       </c>
     </row>
-    <row r="945" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
         <v>2830</v>
       </c>
@@ -20528,7 +20531,7 @@
         <v>2832</v>
       </c>
     </row>
-    <row r="946" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
         <v>2833</v>
       </c>
@@ -20539,7 +20542,7 @@
         <v>2835</v>
       </c>
     </row>
-    <row r="947" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
         <v>2836</v>
       </c>
@@ -20550,7 +20553,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="948" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
         <v>2839</v>
       </c>
@@ -20561,7 +20564,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="949" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
         <v>2842</v>
       </c>
@@ -20572,7 +20575,7 @@
         <v>2844</v>
       </c>
     </row>
-    <row r="950" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
         <v>2845</v>
       </c>
@@ -20583,7 +20586,7 @@
         <v>2847</v>
       </c>
     </row>
-    <row r="951" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
         <v>2848</v>
       </c>
@@ -20594,7 +20597,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="952" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
         <v>2851</v>
       </c>
@@ -20605,7 +20608,7 @@
         <v>2853</v>
       </c>
     </row>
-    <row r="953" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
         <v>2854</v>
       </c>
@@ -20616,7 +20619,7 @@
         <v>3255</v>
       </c>
     </row>
-    <row r="954" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
         <v>2856</v>
       </c>
@@ -20627,7 +20630,7 @@
         <v>2858</v>
       </c>
     </row>
-    <row r="955" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
         <v>2859</v>
       </c>
@@ -20638,7 +20641,7 @@
         <v>2861</v>
       </c>
     </row>
-    <row r="956" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
         <v>2862</v>
       </c>
@@ -20649,7 +20652,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="957" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
         <v>2865</v>
       </c>
@@ -20660,7 +20663,7 @@
         <v>2867</v>
       </c>
     </row>
-    <row r="958" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
         <v>2868</v>
       </c>
@@ -20671,7 +20674,7 @@
         <v>2870</v>
       </c>
     </row>
-    <row r="959" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
         <v>2871</v>
       </c>
@@ -20682,7 +20685,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="960" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
         <v>2874</v>
       </c>
@@ -20693,7 +20696,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="961" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
         <v>2877</v>
       </c>
@@ -20704,7 +20707,7 @@
         <v>2879</v>
       </c>
     </row>
-    <row r="962" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
         <v>2880</v>
       </c>
@@ -20715,7 +20718,7 @@
         <v>2882</v>
       </c>
     </row>
-    <row r="963" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
         <v>2883</v>
       </c>
@@ -20726,7 +20729,7 @@
         <v>2885</v>
       </c>
     </row>
-    <row r="964" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
         <v>2886</v>
       </c>
@@ -20737,7 +20740,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="965" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
         <v>2889</v>
       </c>
@@ -20748,7 +20751,7 @@
         <v>2891</v>
       </c>
     </row>
-    <row r="966" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
         <v>2892</v>
       </c>
@@ -20759,7 +20762,7 @@
         <v>2894</v>
       </c>
     </row>
-    <row r="967" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
         <v>2895</v>
       </c>
@@ -20770,7 +20773,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="968" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
         <v>2898</v>
       </c>
@@ -20781,7 +20784,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="969" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
         <v>2901</v>
       </c>
@@ -20792,7 +20795,7 @@
         <v>2903</v>
       </c>
     </row>
-    <row r="970" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
         <v>2904</v>
       </c>
@@ -20803,7 +20806,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="971" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
         <v>2907</v>
       </c>
@@ -20814,7 +20817,7 @@
         <v>2909</v>
       </c>
     </row>
-    <row r="972" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
         <v>2910</v>
       </c>
@@ -20825,7 +20828,7 @@
         <v>2912</v>
       </c>
     </row>
-    <row r="973" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
         <v>2913</v>
       </c>
@@ -20836,7 +20839,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="974" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
         <v>2916</v>
       </c>
@@ -20847,7 +20850,7 @@
         <v>2918</v>
       </c>
     </row>
-    <row r="975" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
         <v>2919</v>
       </c>
@@ -20858,7 +20861,7 @@
         <v>2921</v>
       </c>
     </row>
-    <row r="976" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
         <v>2922</v>
       </c>
@@ -20869,7 +20872,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="977" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
         <v>2925</v>
       </c>
@@ -20880,7 +20883,7 @@
         <v>2927</v>
       </c>
     </row>
-    <row r="978" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
         <v>2928</v>
       </c>
@@ -20891,7 +20894,7 @@
         <v>2930</v>
       </c>
     </row>
-    <row r="979" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
         <v>2931</v>
       </c>
@@ -20902,7 +20905,7 @@
         <v>2933</v>
       </c>
     </row>
-    <row r="980" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
         <v>2934</v>
       </c>
@@ -20913,7 +20916,7 @@
         <v>2936</v>
       </c>
     </row>
-    <row r="981" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
         <v>2937</v>
       </c>
@@ -20924,7 +20927,7 @@
         <v>2939</v>
       </c>
     </row>
-    <row r="982" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
         <v>2940</v>
       </c>
@@ -20935,7 +20938,7 @@
         <v>2942</v>
       </c>
     </row>
-    <row r="983" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
         <v>2943</v>
       </c>
@@ -20946,7 +20949,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="984" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
         <v>2946</v>
       </c>
@@ -20957,7 +20960,7 @@
         <v>2948</v>
       </c>
     </row>
-    <row r="985" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
         <v>2949</v>
       </c>
@@ -20968,7 +20971,7 @@
         <v>2951</v>
       </c>
     </row>
-    <row r="986" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
         <v>2952</v>
       </c>
@@ -20979,7 +20982,7 @@
         <v>2954</v>
       </c>
     </row>
-    <row r="987" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
         <v>2955</v>
       </c>
@@ -20990,7 +20993,7 @@
         <v>2957</v>
       </c>
     </row>
-    <row r="988" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
         <v>2958</v>
       </c>
@@ -21001,7 +21004,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="989" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A989" t="s">
         <v>2961</v>
       </c>
@@ -21012,7 +21015,7 @@
         <v>2963</v>
       </c>
     </row>
-    <row r="990" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
         <v>2964</v>
       </c>
@@ -21023,7 +21026,7 @@
         <v>2966</v>
       </c>
     </row>
-    <row r="991" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
         <v>2967</v>
       </c>
@@ -21034,7 +21037,7 @@
         <v>2969</v>
       </c>
     </row>
-    <row r="992" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
         <v>2970</v>
       </c>
@@ -21045,7 +21048,7 @@
         <v>2972</v>
       </c>
     </row>
-    <row r="993" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
         <v>2973</v>
       </c>
@@ -21056,7 +21059,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="994" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
         <v>2976</v>
       </c>
@@ -21067,7 +21070,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="995" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A995" t="s">
         <v>2979</v>
       </c>
@@ -21078,7 +21081,7 @@
         <v>2981</v>
       </c>
     </row>
-    <row r="996" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
         <v>2982</v>
       </c>
@@ -21089,7 +21092,7 @@
         <v>2984</v>
       </c>
     </row>
-    <row r="997" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
         <v>2985</v>
       </c>
@@ -21100,7 +21103,7 @@
         <v>2987</v>
       </c>
     </row>
-    <row r="998" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
         <v>2988</v>
       </c>
@@ -21111,7 +21114,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="999" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
         <v>2991</v>
       </c>
@@ -21122,7 +21125,7 @@
         <v>2993</v>
       </c>
     </row>
-    <row r="1000" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1000" t="s">
         <v>2994</v>
       </c>
@@ -21133,7 +21136,7 @@
         <v>2996</v>
       </c>
     </row>
-    <row r="1001" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1001" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
         <v>2997</v>
       </c>
@@ -21144,7 +21147,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="1002" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1002" t="s">
         <v>3000</v>
       </c>
@@ -21155,7 +21158,7 @@
         <v>3002</v>
       </c>
     </row>
-    <row r="1003" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1003" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1003" t="s">
         <v>3003</v>
       </c>
@@ -21166,7 +21169,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="1004" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1004" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1004" t="s">
         <v>3006</v>
       </c>
@@ -21177,7 +21180,7 @@
         <v>3008</v>
       </c>
     </row>
-    <row r="1005" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1005" t="s">
         <v>3009</v>
       </c>
@@ -21188,7 +21191,7 @@
         <v>3011</v>
       </c>
     </row>
-    <row r="1006" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1006" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1006" t="s">
         <v>3012</v>
       </c>
@@ -21199,7 +21202,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="1007" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1007" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1007" t="s">
         <v>3015</v>
       </c>
@@ -21210,7 +21213,7 @@
         <v>3017</v>
       </c>
     </row>
-    <row r="1008" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1008" t="s">
         <v>3018</v>
       </c>
@@ -21221,7 +21224,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="1009" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1009" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1009" t="s">
         <v>3021</v>
       </c>
@@ -21232,7 +21235,7 @@
         <v>3023</v>
       </c>
     </row>
-    <row r="1010" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1010" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1010" t="s">
         <v>3024</v>
       </c>
@@ -21243,7 +21246,7 @@
         <v>3026</v>
       </c>
     </row>
-    <row r="1011" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1011" t="s">
         <v>3027</v>
       </c>
@@ -21254,7 +21257,7 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="1012" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1012" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1012" t="s">
         <v>3030</v>
       </c>
@@ -21265,7 +21268,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="1013" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1013" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1013" t="s">
         <v>3033</v>
       </c>
@@ -21276,7 +21279,7 @@
         <v>3035</v>
       </c>
     </row>
-    <row r="1014" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1014" t="s">
         <v>3036</v>
       </c>
@@ -21287,7 +21290,7 @@
         <v>3038</v>
       </c>
     </row>
-    <row r="1015" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1015" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1015" t="s">
         <v>3039</v>
       </c>
@@ -21298,7 +21301,7 @@
         <v>3041</v>
       </c>
     </row>
-    <row r="1016" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1016" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1016" t="s">
         <v>3042</v>
       </c>
@@ -21309,7 +21312,7 @@
         <v>3044</v>
       </c>
     </row>
-    <row r="1017" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1017" t="s">
         <v>3045</v>
       </c>
@@ -21320,7 +21323,7 @@
         <v>3047</v>
       </c>
     </row>
-    <row r="1018" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1018" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1018" t="s">
         <v>3048</v>
       </c>
@@ -21331,7 +21334,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="1019" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1019" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1019" t="s">
         <v>3051</v>
       </c>
@@ -21342,7 +21345,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="1020" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1020" t="s">
         <v>3054</v>
       </c>
@@ -21353,7 +21356,7 @@
         <v>3056</v>
       </c>
     </row>
-    <row r="1021" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1021" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1021" t="s">
         <v>3057</v>
       </c>
@@ -21364,7 +21367,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="1022" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1022" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1022" t="s">
         <v>3060</v>
       </c>
@@ -21375,7 +21378,7 @@
         <v>3062</v>
       </c>
     </row>
-    <row r="1023" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1023" t="s">
         <v>3063</v>
       </c>
@@ -21386,7 +21389,7 @@
         <v>3065</v>
       </c>
     </row>
-    <row r="1024" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1024" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1024" t="s">
         <v>3066</v>
       </c>
@@ -21397,7 +21400,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="1025" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1025" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1025" t="s">
         <v>3069</v>
       </c>
@@ -21408,7 +21411,7 @@
         <v>3071</v>
       </c>
     </row>
-    <row r="1026" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1026" t="s">
         <v>3072</v>
       </c>
@@ -21419,7 +21422,7 @@
         <v>3074</v>
       </c>
     </row>
-    <row r="1027" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1027" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1027" t="s">
         <v>3075</v>
       </c>
@@ -21430,7 +21433,7 @@
         <v>3077</v>
       </c>
     </row>
-    <row r="1028" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1028" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1028" t="s">
         <v>3078</v>
       </c>
@@ -21441,7 +21444,7 @@
         <v>3080</v>
       </c>
     </row>
-    <row r="1029" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1029" t="s">
         <v>3081</v>
       </c>
@@ -21452,7 +21455,7 @@
         <v>3083</v>
       </c>
     </row>
-    <row r="1030" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1030" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1030" t="s">
         <v>3084</v>
       </c>
@@ -21463,7 +21466,7 @@
         <v>3086</v>
       </c>
     </row>
-    <row r="1031" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1031" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1031" t="s">
         <v>3087</v>
       </c>
@@ -21474,7 +21477,7 @@
         <v>3089</v>
       </c>
     </row>
-    <row r="1032" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1032" t="s">
         <v>3090</v>
       </c>
@@ -21485,7 +21488,7 @@
         <v>3092</v>
       </c>
     </row>
-    <row r="1033" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1033" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1033" t="s">
         <v>3093</v>
       </c>
@@ -21496,7 +21499,7 @@
         <v>3095</v>
       </c>
     </row>
-    <row r="1034" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1034" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1034" t="s">
         <v>3096</v>
       </c>
@@ -21507,7 +21510,7 @@
         <v>3098</v>
       </c>
     </row>
-    <row r="1035" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1035" t="s">
         <v>3099</v>
       </c>
@@ -21518,7 +21521,7 @@
         <v>3101</v>
       </c>
     </row>
-    <row r="1036" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1036" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1036" t="s">
         <v>3102</v>
       </c>
@@ -21529,7 +21532,7 @@
         <v>3104</v>
       </c>
     </row>
-    <row r="1037" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1037" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1037" t="s">
         <v>3105</v>
       </c>
@@ -21540,7 +21543,7 @@
         <v>3107</v>
       </c>
     </row>
-    <row r="1038" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1038" t="s">
         <v>3108</v>
       </c>
@@ -21551,7 +21554,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="1039" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1039" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1039" t="s">
         <v>3111</v>
       </c>
@@ -21562,7 +21565,7 @@
         <v>3113</v>
       </c>
     </row>
-    <row r="1040" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1040" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1040" t="s">
         <v>3114</v>
       </c>
@@ -21573,7 +21576,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="1041" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1041" t="s">
         <v>3117</v>
       </c>
@@ -21584,7 +21587,7 @@
         <v>3119</v>
       </c>
     </row>
-    <row r="1042" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1042" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
         <v>3120</v>
       </c>
@@ -21595,7 +21598,7 @@
         <v>3122</v>
       </c>
     </row>
-    <row r="1043" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1043" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1043" t="s">
         <v>3123</v>
       </c>
@@ -21606,7 +21609,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="1044" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1044" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1044" t="s">
         <v>3126</v>
       </c>
@@ -21617,7 +21620,7 @@
         <v>3128</v>
       </c>
     </row>
-    <row r="1045" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1045" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1045" t="s">
         <v>3129</v>
       </c>
@@ -21628,7 +21631,7 @@
         <v>3131</v>
       </c>
     </row>
-    <row r="1046" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1046" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1046" t="s">
         <v>3132</v>
       </c>
@@ -21639,7 +21642,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="1047" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1047" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1047" t="s">
         <v>3135</v>
       </c>
@@ -21650,7 +21653,7 @@
         <v>3137</v>
       </c>
     </row>
-    <row r="1048" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1048" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1048" t="s">
         <v>3138</v>
       </c>
@@ -21661,7 +21664,7 @@
         <v>3140</v>
       </c>
     </row>
-    <row r="1049" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1049" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1049" t="s">
         <v>3141</v>
       </c>
@@ -21672,7 +21675,7 @@
         <v>3143</v>
       </c>
     </row>
-    <row r="1050" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1050" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1050" t="s">
         <v>3144</v>
       </c>
@@ -21683,7 +21686,7 @@
         <v>3146</v>
       </c>
     </row>
-    <row r="1051" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1051" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1051" t="s">
         <v>3147</v>
       </c>
@@ -21694,7 +21697,7 @@
         <v>3149</v>
       </c>
     </row>
-    <row r="1052" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1052" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1052" t="s">
         <v>3150</v>
       </c>
@@ -21705,7 +21708,7 @@
         <v>3152</v>
       </c>
     </row>
-    <row r="1053" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1053" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1053" t="s">
         <v>3153</v>
       </c>
@@ -21716,7 +21719,7 @@
         <v>3155</v>
       </c>
     </row>
-    <row r="1054" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1054" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1054" t="s">
         <v>3156</v>
       </c>
@@ -21727,7 +21730,7 @@
         <v>3158</v>
       </c>
     </row>
-    <row r="1055" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1055" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1055" t="s">
         <v>3159</v>
       </c>
@@ -21738,7 +21741,7 @@
         <v>3161</v>
       </c>
     </row>
-    <row r="1056" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1056" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1056" t="s">
         <v>3162</v>
       </c>
@@ -21749,7 +21752,7 @@
         <v>3164</v>
       </c>
     </row>
-    <row r="1057" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1057" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1057" t="s">
         <v>3165</v>
       </c>
@@ -21760,7 +21763,7 @@
         <v>3167</v>
       </c>
     </row>
-    <row r="1058" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1058" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1058" t="s">
         <v>3168</v>
       </c>
@@ -21771,7 +21774,7 @@
         <v>3170</v>
       </c>
     </row>
-    <row r="1059" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1059" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1059" t="s">
         <v>3171</v>
       </c>
@@ -21782,7 +21785,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="1060" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1060" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1060" t="s">
         <v>3174</v>
       </c>
@@ -21793,7 +21796,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="1061" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1061" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1061" t="s">
         <v>3177</v>
       </c>
@@ -21804,7 +21807,7 @@
         <v>3179</v>
       </c>
     </row>
-    <row r="1062" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1062" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1062" t="s">
         <v>3180</v>
       </c>
@@ -21815,7 +21818,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="1063" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1063" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1063" t="s">
         <v>3183</v>
       </c>
@@ -21826,7 +21829,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="1064" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1064" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1064" t="s">
         <v>3186</v>
       </c>
@@ -21837,7 +21840,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="1065" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1065" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1065" t="s">
         <v>3189</v>
       </c>
@@ -21848,7 +21851,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="1066" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1066" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1066" t="s">
         <v>3192</v>
       </c>
@@ -21859,7 +21862,7 @@
         <v>3194</v>
       </c>
     </row>
-    <row r="1067" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1067" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1067" t="s">
         <v>3195</v>
       </c>
@@ -21870,7 +21873,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="1068" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1068" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1068" t="s">
         <v>3198</v>
       </c>
@@ -21881,7 +21884,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="1069" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1069" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1069" t="s">
         <v>3201</v>
       </c>
@@ -21892,7 +21895,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="1070" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1070" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1070" t="s">
         <v>3204</v>
       </c>
@@ -21903,7 +21906,7 @@
         <v>3206</v>
       </c>
     </row>
-    <row r="1071" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1071" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1071" t="s">
         <v>3207</v>
       </c>
@@ -21914,7 +21917,7 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="1072" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1072" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1072" t="s">
         <v>3210</v>
       </c>
@@ -21925,7 +21928,7 @@
         <v>3212</v>
       </c>
     </row>
-    <row r="1073" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1073" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1073" t="s">
         <v>3213</v>
       </c>
@@ -21936,7 +21939,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="1074" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1074" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1074" t="s">
         <v>3216</v>
       </c>
@@ -21947,7 +21950,7 @@
         <v>3218</v>
       </c>
     </row>
-    <row r="1075" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1075" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1075" t="s">
         <v>3219</v>
       </c>
@@ -21958,7 +21961,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="1076" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1076" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1076" t="s">
         <v>3222</v>
       </c>
@@ -21969,7 +21972,7 @@
         <v>3224</v>
       </c>
     </row>
-    <row r="1077" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1077" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1077" t="s">
         <v>3225</v>
       </c>
@@ -21980,7 +21983,7 @@
         <v>3227</v>
       </c>
     </row>
-    <row r="1078" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1078" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1078" t="s">
         <v>3228</v>
       </c>
@@ -21991,7 +21994,7 @@
         <v>3230</v>
       </c>
     </row>
-    <row r="1079" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1079" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1079" t="s">
         <v>3231</v>
       </c>
@@ -22002,7 +22005,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="1080" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1080" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1080" t="s">
         <v>3234</v>
       </c>
@@ -22013,7 +22016,7 @@
         <v>3236</v>
       </c>
     </row>
-    <row r="1081" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1081" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1081" t="s">
         <v>3237</v>
       </c>
@@ -22024,7 +22027,7 @@
         <v>3239</v>
       </c>
     </row>
-    <row r="1082" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1082" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1082" t="s">
         <v>3240</v>
       </c>
@@ -22035,7 +22038,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="1083" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1083" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1083" t="s">
         <v>3243</v>
       </c>
@@ -22046,7 +22049,7 @@
         <v>3245</v>
       </c>
     </row>
-    <row r="1084" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1084" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1084" t="s">
         <v>3246</v>
       </c>
@@ -22057,7 +22060,7 @@
         <v>3248</v>
       </c>
     </row>
-    <row r="1085" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1085" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1085" t="s">
         <v>3249</v>
       </c>
@@ -22068,7 +22071,7 @@
         <v>3251</v>
       </c>
     </row>
-    <row r="1086" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1086" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1086" t="s">
         <v>3252</v>
       </c>
